--- a/data/03_output/evaluaciones/auditoria_manual_1_BoW.xlsx
+++ b/data/03_output/evaluaciones/auditoria_manual_1_BoW.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>¿Cómo se clasifican los tipos de crédito de la Cartera Crediticia de Consumo no Revolvente para el cálculo de reservas?</t>
+          <t>¿Para consumo no revolvente cómo se define el pago realizado?</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,12 +464,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>al Incumplimiento (EI) de cada crédito de la Cartera Crediticia de Consumo no Revolvente será igual al Saldo del Crédito (S) al momento de la calificación de la cartera.</t>
+          <t>por concepto de créditos de la Cartera de Consumo No Revolvente.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ABCD (B) | A los créditos que sean otorgados a personas físicas y cuyo destino sea la adquisición de bienes de consumo duradero</t>
+          <t>Monto correspondiente a la suma de los pagos realizados por el acreditado en el Periodo de Facturación</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>¿Cómo pueden las instituciones financieras utilizar las garantías reales financieras para reducir las reservas preventivas según el Artículo 97 Bis 6?</t>
+          <t>¿Qué se consideraría un crédito personal?</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -660,12 +660,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>reconocimiento de las garantías reales financieras, dicho ajuste se realizará conforme al Artículo 97 Bis 6 de la CUB.</t>
+          <t>Crédito OTROS. A cualquier otro crédito al consumo no revolvente, diferente a las categorías ABCD, AUTO, MICROCRÉDITOS, NOMINA y PERSONAL.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras</t>
+          <t>A los créditos que sean cobrados por la Institución por cualquier medio de pago distinto de la cuenta de nómina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>¿Qué enfoques pueden adoptar las instituciones para el cálculo de reservas preventivas y cuáles son sus requisitos?</t>
+          <t>¿Qué se entiendo por saldo a pagar?</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -743,13 +743,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Las Instituciones, podrán optar por alguno de los enfoques siguientes:  
-I. El Enfoque Estándar, el cual resulta aplicable a todas las carteras consideradas en la definición de Cartera Crediticia contenida en el Artículo 1 de las presentes disposiciones. Las Instituciones que adopten este enfoque para el cálculo de sus reservas preventivas deberán sujetarse a los requisitos y procedimientos contenidos dentro del Capítulo V Bis.</t>
+          <t>$\% USO_i = \text{Saldo a Pagar} / \text{Límite de Crédito}$  
+$\mathbf{Var}_{\beta 4} = \quad \% \mathbf{PAGO}_i = \quad$ Porcentaje que representa el Pago Realizado respecto al Saldo a Pagar.  
+$\% PAGO_i = \text{Pago Realizado} / \text{Saldo a Pagar}$</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Las Instituciones, podrán optar por alguno de los enfoques siguientes: I. El Enfoque Estándar... II. El Enfoque Interno...</t>
+          <t>Importe exigible de la deuda a la fecha de corte en la cual inicia el Periodo de Pago que el acreditado tiene por pagar a la Institución</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -762,7 +763,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>¿Cómo se determina la Probabilidad de Incumplimiento para créditos clasificados como "B" en la Cartera Crediticia de Consumo no Revolvente?</t>
+          <t>¿Cómo se determina la reservas para los créditos en etapa 2?</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -770,12 +771,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>por concepto de créditos de la Cartera de Consumo No Revolvente.</t>
+          <t>Los cálculos requeridos para obtener las reservas para la vida completa de los créditos deberán realizarse considerando cuatro decimales.  
+El monto de reservas para los créditos en etapa 2 será el resultado de:  
+$$
+\ Reservas\ Etapa\ 2_i = \max\left(\text{Reservas\ Vida\ Completa}_i, PI_i^X \times SP_i^X \times EI_i^X\right)
+$$  
+El monto total de reservas a constituir por la Institución para esta cartera, será igual a la sumatoria de las reservas de cada crédito.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>La Probabilidad de Incumplimiento de los créditos de la Cartera Crediticia de Consumo no Revolvente clasificados como “B” deberá obtenerse conforme a lo siguiente: a) Si $ATR_{i}^{B} &gt; 3$ o cuando el crédito se encuentre en etapa 3: PI_{i}^{B} = 100%</t>
+          <t>Reservas\ Etapa\ 2_i = \max\left(\text{Reservas\ Vida\ Completa}_i, PI_i^X \times SP_i^X \times EI_i^X\right)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -817,7 +823,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>¿Qué criterios deben seguir las instituciones para migrar un crédito entre etapas de riesgo?</t>
+          <t>¿Se pueden reportar tasas de interés en cero?</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -825,13 +831,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>| 21 | Financiamiento en etapas 1 y 2 otorgado a contrapartes distintas de entidades financieras con un ponderador de riesgo de crédito menor o igual a 35% de acuerdo al Método Estándar para riesgo de crédito de Basilea II. |
-| 22 | Cartera de crédito de vivienda en etapas 1 y 2. |</t>
+          <t>### Artículo 37.- Información sobre las tasas de interés</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los criterios bajo los cuales las Instituciones podrán realizar dicha migración deberán estar formalizados dentro de los manuales de políticas y procedimientos de la Institución y deberán ser aplicados de forma consistente.</t>
+          <t>En casos donde la tasa de interés anual sea igual a cero, se deberá utilizar un valor fijo de 0.00001%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -844,7 +849,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>¿Cómo se determina la Probabilidad de Incumplimiento para créditos con ACT_i ≤ 3?</t>
+          <t>¿Cuándo no exista información del acreditado en las sociedades de información crediticia que factor de riesgo se aplica?</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -852,15 +857,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>### Artículo 91 Bis 1.- La Probabilidad de Incumplimiento de los créditos clasificados como “B, A, N, P u O” conforme al Artículo 91 Bis de las presentes disposiciones, se determinará de acuerdo con las fracciones I a V siguientes, según corresponda:  
-I. La Probabilidad de Incumplimiento de los créditos de la Cartera Crediticia de Consumo no Revolvente clasificados como “B” deberá obtenerse conforme a lo siguiente:  
-a) Si $ATR_{i}^{B} &amp;gt; 3$ o cuando el crédito se encuentre en etapa 3:  
-$$</t>
+          <t>OTROS (VECES Conforme al Art. 91 Bis 1 fracción V de la CUB).- El cociente del Monto a Pagar Reportado en las Sociedades de Información Crediticia entre el Saldo Reportado en las Sociedades de Información Crediticia a la fecha de calificación, de conformidad con el Artículo 91 de la CUB. Cuando no exista información de la persona acreditada en las sociedades de información crediticia esta variable deberá de tomar el valor de 0.5, por otro lado, cuando no se hubiese consultado la totalidad de la</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PI_i = \frac{1}{1 + e^{-Z_i}}</t>
+          <t>Cuando no exista información del acreditado en las sociedades de información crediticia autorizadas, las Instituciones para realizar el cálculo de las variables...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -873,7 +875,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>¿Cómo pueden las instituciones financieras reducir las reservas preventivas a través del reconocimiento de garantías?</t>
+          <t>¿Cuál es la fórmula regulatoria para calcular el Coeficiente de Cobertura de Liquidez y cómo debe expresarse el resultado porcentual?</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -881,12 +883,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>### Artículo 97 Bis 6.- Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito, con la finalidad de disminuir las reservas preventivas derivadas de la calificación de cartera de los créditos a los que se refiere la presente sección. Para tal efecto, emplearán</t>
+          <t># TÍTULO II
+COEFICIENTE DE COBERTURA DE LIQUIDEZ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito, con la finalidad de disminuir las reservas preventivas</t>
+          <t>El Coeficiente de Cobertura de Liquidez será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -899,93 +902,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>¿Qué tipos de garantías son reconocidos para la estimación de la Severidad de la Pérdida de los créditos?</t>
+          <t>¿Cómo se determina el flujo de salida contingente por operaciones con instrumentos financieros derivados?</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
-        <is>
-          <t>| 4 | 15 | La severidad de la pérdida ajustada debe ser menor o igual que la severidad de la pérdida de la persona acreditada. | 3 |
-| 4 | 16 | Las reservas totales para el portafolio sin reconocimiento de garantías solo aplican en créditos con garantías de Primeras Perdidas relativas a la persona garante. | 3 |</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Q18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>¿En qué condiciones deben las instituciones aplicar el apartado E para calcular sus reservas?</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>## Apartado E</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>emplearán el presente apartado siempre que calculen sus reservas con la metodología de calificación de cartera a la que se refiere esta sección</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Q19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>¿Cuál es la fórmula regulatoria para calcular el Coeficiente de Cobertura de Liquidez y cómo debe expresarse el resultado porcentual?</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t># TÍTULO II
-COEFICIENTE DE COBERTURA DE LIQUIDEZ</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>El Coeficiente de Cobertura de Liquidez será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Q20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>¿Cómo se determina el flujo de salida contingente por operaciones con instrumentos financieros derivados?</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
         <is>
           <t>- **SDis** Flujo de salida por operaciones con instrumentos financieros derivados con la contraparte i compensando por subyacente.
 - **SND** Flujo de salida por operaciones con instrumentos financieros derivados.
@@ -993,111 +916,111 @@
 - **SNDs** Flujo de salida por operaciones con instrumentos financieros derivados compensando por subyacente.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Las Instituciones deberán calcular el flujo de salida contingente por operaciones con instrumentos financieros derivados como el máximo valor absoluto de la suma de los montos referidos en los incisos a) y b) siguientes</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Q21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>¿Cómo se calcula el flujo total de entrada de efectivo?</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>V. El flujo total de entrada de efectivo será el monto que resulte menor entre: i) la suma de todos los flujos de entrada de efectivo calculados de conformidad con la fracción I anterior, y ii) el  
 75 por ciento del flujo total de salida de efectivo calculado conforme el artículo 11 de las presentes disposiciones.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>El flujo total de entrada de efectivo será el monto que resulte menor entre: i) la suma de todos los flujos de entrada de efectivo calculados de conformidad con la fracción I anterior, y ii) el 75 por ciento del flujo total de salida de efectivo</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>¿Qué factor de salida se aplica a depósitos en cuentas transaccionales de personas físicas cubiertos por el IPAB?</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>| | operaciones pasivas garantizadas por el IPAB o el que corresponda en la jurisdicción en que se hayan constituido las cuentas. | |
 | --- | --- | --- |
 | | I.1.3 Depósitos de personas físicas y personas físicas con actividad empresarial en cuentas distintas de Cuentas Transaccionales. | 10% |</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>I.1.2.1 Monto que no excede el límite establecido en la Ley para la Protección al Ahorro Bancario para las operaciones pasivas garantizadas por el IPAB</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Q23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>¿Cómo se registran las operaciones de compra-venta fecha valor para calcular el coeficiente de cobertura de liquidez?</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>| IV | Operaciones cambiarias fecha valor y operaciones de compra-venta de títulos fecha valor, cuando resulte una posición activa una vez compensada la parte activa y pasiva de cada operación. | 100% |
 | V | Otras operaciones: | |
 | | V.1 Parte no dispuesta de las Líneas de Crédito a favor de la Institución que no hubiesen sido dispuestas. | 0% |</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Compensar para cada operación de compra venta de títulos pactada a una fecha valor, la parte activa y pasiva de la misma operación e incluir el monto resultante como flujo de entrada</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Q24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>¿Cuál es la fórmula regulatoria para calcular el Coeficiente de Financiamiento Estable Neto y cómo debe expresarse el resultado porcentual?</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>El Coeficiente de Financiamiento Estable Neto será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.  
 $$
@@ -1105,108 +1028,108 @@
 $$</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>El Coeficiente de Financiamiento Estable Neto será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Q25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>¿Con qué periodicidad debe reportarse el CFEN al Banco de México y a qué fecha de cálculo corresponde?</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>BANCO DE MÉXICO®</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>El Coeficiente de Financiamiento Estable Neto que corresponda al último Día Hábil de cada mes deberá reportarse durante los primeros dieciséis Días Hábiles del mes inmediato siguiente.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Q26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>¿Qué se entiende por Monto de Financiamiento Estable Disponible para efectos del CFEN?</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Para determinar el importe por operaciones con instrumentos financieros derivados en el cálculo de los componentes del Coeficiente de Financiamiento Estable Neto; es decir, para determinar el Monto de Financiamiento Estable Requerido y el Monto de Financiamiento Estable Disponible, las Instituciones deberán aplicar la metodología señalada en el presente anexo para cada contraparte.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Monto de Financiamiento Estable Disponible: al monto que resulte de sumar los pasivos y capital señalados en el Anexo 6 de las presentes disposiciones</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Q27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>¿Qué se entiende por Monto de Financiamiento Estable Requerido para efectos del CFEN?</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t># ANEXO 7  
 Monto de Financiamiento Estable Requerido para activos no restringidos y otras operaciones  
 Las Instituciones, para determinar el Monto de Financiamiento Estable Requerido para activos no restringidos y otras operaciones, deberán observar lo siguiente:</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Monto de Financiamiento Estable Requerido: al monto que resulte de sumar: (i) los activos no restringidos y otras operaciones señaladas en el Anexo 7 de las presentes disposiciones</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Q28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>¿Qué factor de financiamiento estable disponible se asigna al capital fundamental, capital básico no fundamental y pasivos con plazo residual igual o mayor a un año?</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>| | | Sin vencimiento | &lt; 6 meses | De 6 meses a &lt; 1 año | | ≥1 año | Sin vencimiento | &lt; 6 meses | De 6 meses a &lt; 1 año | ≥1 año | |
 | ELEMENTOS DEL MONTO DE FINANCIAMIENTO ESTABLE DISPONIBLE | | | | | | | | | | | |
@@ -1217,9 +1140,89 @@
 | 5 | Depósitos estables. | | | | | | | | | | |</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Los factores para la determinación del financiamiento estable disponible serán: I. Pasivos y capital con factor del 100% A. Capital fundamental</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>¿Cuál es la definición de liquidez intradía según las herramientas de monitoreo del Comité de Basilea?</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t># III. Herramientas de monitoreo de la liquidez intradía</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Liquidez intradía: fondos a los que se puede acceder durante el día hábil, usualmente para permitir que los bancos realicen pagos en tiempo real;</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>¿Cuáles son las principales fuentes propias de liquidez intradía que puede utilizar un banco durante el día hábil?</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>## (2) Liquidez intradía disponible al inicio del día hábil en relación con el impacto de tensiones intradía sobre el uso diario de liquidez del banco  
+Si el impacto de una tensión de liquidez intradía sobre el uso diario de liquidez de un banco es grande en relación con su liquidez intradía disponible al inicio del día hábil, ello sugiere que el banco podría tener dificultades para liquidar pagos de manera oportuna en condiciones de tensión.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>(i) Fuentes Fuentes propias - Saldos de reserva en el banco central; - Colateral pignorado con el banco central o con sistemas auxiliares</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>¿Cómo se define un escenario de tensión de contraparte?</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>32. Una tensión de contraparte puede provocar que los participantes directos y los bancos que utilizan servicios de corresponsalía bancaria no puedan depender de los pagos entrantes de la contraparte estresada, reduciendo la disponibilidad de liquidez intradía que puede obtenerse mediante la recepción de pagos de dicha contraparte.  
+(iii) Tensión de un banco cliente: un banco cliente de un banco corresponsal sufre un evento de tensión</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Los factores para la determinación del financiamiento estable disponible serán: I. Pasivos y capital con factor del 100% A. Capital fundamental</t>
+          <t>(ii) Tensión de contraparte: una contraparte importante sufre un evento de tensión intradía que le impide realizar pagos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1232,93 +1235,13 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>¿Cuál es la definición de liquidez intradía según las herramientas de monitoreo del Comité de Basilea?</t>
+          <t>¿Cómo se calcula el uso máximo diario de liquidez intradía a partir de la posición neta acumulada de pagos enviados y recibidos?</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
-        <is>
-          <t># III. Herramientas de monitoreo de la liquidez intradía</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Liquidez intradía: fondos a los que se puede acceder durante el día hábil, usualmente para permitir que los bancos realicen pagos en tiempo real;</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Q30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>¿Cuáles son las principales fuentes propias de liquidez intradía que puede utilizar un banco durante el día hábil?</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>## (2) Liquidez intradía disponible al inicio del día hábil en relación con el impacto de tensiones intradía sobre el uso diario de liquidez del banco  
-Si el impacto de una tensión de liquidez intradía sobre el uso diario de liquidez de un banco es grande en relación con su liquidez intradía disponible al inicio del día hábil, ello sugiere que el banco podría tener dificultades para liquidar pagos de manera oportuna en condiciones de tensión.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>(i) Fuentes Fuentes propias - Saldos de reserva en el banco central; - Colateral pignorado con el banco central o con sistemas auxiliares</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Q31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>¿Cómo se define un escenario de tensión de contraparte?</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>32. Una tensión de contraparte puede provocar que los participantes directos y los bancos que utilizan servicios de corresponsalía bancaria no puedan depender de los pagos entrantes de la contraparte estresada, reduciendo la disponibilidad de liquidez intradía que puede obtenerse mediante la recepción de pagos de dicha contraparte.  
-(iii) Tensión de un banco cliente: un banco cliente de un banco corresponsal sufre un evento de tensión</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>(ii) Tensión de contraparte: una contraparte importante sufre un evento de tensión intradía que le impide realizar pagos</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Q32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>¿Cómo se calcula el uso máximo diario de liquidez intradía a partir de la posición neta acumulada de pagos enviados y recibidos?</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
         <is>
           <t>Figura 1. Uso máximo diario de liquidez intradía  
 Herramientas de monitoreo para la gestión de la liquidez intradía - traducción al español
@@ -1326,39 +1249,39 @@
 La figura ilustra una trayectoria de posición neta acumulada durante el día: el mayor valor positivo corresponde a la posición neta acumulada positiva más alta, mientras que el punto más bajo corresponde a la mayor posición neta acumulada negativa. En el ejemplo, el uso de liquidez intradía equivale a 10 unidades.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>(i) Uso máximo diario de liquidez intradía 13. Esta herramienta permitirá a los supervisores monitorear el uso de liquidez intradía de un banco en condiciones normales.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Q33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>¿Qué son las obligaciones con horario específico y por qué su incumplimiento puede generar riesgo financiero o reputacional?</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>## (iv) Obligaciones con horario específico  
 22. Esta herramienta permitirá a los supervisores comprender mejor las obligaciones con horario específico de un banco. La falta de liquidación oportuna de estas obligaciones podría generar una penalización financiera, daño reputacional para el banco o pérdida de negocio futuro.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>(iv) Obligaciones con horario específico 22. Esta herramienta permitirá a los supervisores comprender mejor las obligaciones con horario específico de un banco.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
